--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553826133</v>
+        <v>46157.93108518888</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108518888</v>
+        <v>46157.93133000669</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93133000669</v>
+        <v>46157.9338096122</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9338096122</v>
+        <v>46157.93691895948</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93691895948</v>
+        <v>46158.28203563035</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203563035</v>
+        <v>46158.29649936371</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29649936371</v>
+        <v>46158.29804346871</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804346871</v>
+        <v>46158.33367862943</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33367862943</v>
+        <v>46158.37219588142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37219588142</v>
+        <v>46158.37274138372</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
